--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4896</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5046</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5220</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2614</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2596</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2614</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2610</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1946</v>
+        <v>5264</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>298</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-fr.xlsx
+++ b/output/tetris-fr.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>22</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
